--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487587_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487587_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1001</v>
+        <v>4.2791</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2941</v>
+        <v>3.5549</v>
       </c>
       <c r="F2" t="n">
-        <v>0.806</v>
+        <v>0.7242</v>
       </c>
       <c r="G2" t="n">
         <v>1.1348</v>
@@ -610,13 +610,13 @@
         <v>2.1344</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7824</v>
+        <v>-0.6034</v>
       </c>
       <c r="T2" t="n">
-        <v>0.111</v>
+        <v>0.3718</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8934</v>
+        <v>-0.9752</v>
       </c>
       <c r="V2" t="n">
         <v>2.7776</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8157</v>
+        <v>1.6022</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4255</v>
+        <v>3.1848</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6099</v>
+        <v>-1.5826</v>
       </c>
       <c r="G3" t="n">
         <v>1.1055</v>
@@ -688,13 +688,13 @@
         <v>1.1642</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9042</v>
+        <v>-0.3093</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2218</v>
+        <v>0.9811</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.3176</v>
+        <v>-1.2903</v>
       </c>
       <c r="V3" t="n">
         <v>0.6119</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. FUENTE DIEZ</t>
+          <t>E. PASCUAL COZAR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2258</v>
+        <v>0.6498</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7216</v>
+        <v>2.1113</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4958</v>
+        <v>-1.4615</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1409</v>
+        <v>1.0711</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3205</v>
+        <v>-0.0717</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1796</v>
+        <v>1.1428</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6942</v>
+        <v>4.2495</v>
       </c>
       <c r="K4" t="n">
-        <v>0.103</v>
+        <v>2.278</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5911999999999999</v>
+        <v>1.9715</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.835</v>
+        <v>-3.1783</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4235</v>
+        <v>-2.3497</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4115</v>
+        <v>-0.8286</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3881</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.194</v>
+        <v>-2.1344</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5821</v>
+        <v>1.7463</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3035</v>
+        <v>-0.3631</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0606</v>
+        <v>0.3261</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2429</v>
+        <v>-0.6892</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2821</v>
+        <v>0.3299</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2821</v>
+        <v>-0.3299</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. PASCUAL COZAR</t>
+          <t>P. FUENTE DIEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0982</v>
+        <v>0.5806</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7505</v>
+        <v>1.0219</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6523</v>
+        <v>-0.4413</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0711</v>
+        <v>-0.1409</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0717</v>
+        <v>-0.3205</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1428</v>
+        <v>0.1796</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2495</v>
+        <v>0.6942</v>
       </c>
       <c r="K5" t="n">
-        <v>2.278</v>
+        <v>0.103</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9715</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.1783</v>
+        <v>-0.835</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.3497</v>
+        <v>-0.4235</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8286</v>
+        <v>-0.4115</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3881</v>
+        <v>0.3881</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1344</v>
+        <v>-0.194</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7463</v>
+        <v>0.5821</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9147999999999999</v>
+        <v>0.0513</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0348</v>
+        <v>0.2397</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.88</v>
+        <v>-0.1884</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3299</v>
+        <v>0.2821</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3299</v>
+        <v>0.2821</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6597</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.1107</v>
+        <v>-2.114</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.7826</v>
+        <v>-2.9222</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6719000000000001</v>
+        <v>0.8082</v>
       </c>
       <c r="G6" t="n">
         <v>0.2603</v>
@@ -922,13 +922,13 @@
         <v>1.3582</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6247</v>
+        <v>-0.6281</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3286</v>
+        <v>0.189</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9533</v>
+        <v>-0.8169999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. HERMOSO ALCUBILLA</t>
+          <t>J. OLIVA SANCHEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.4065</v>
+        <v>-2.8641</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5511</v>
+        <v>-0.2356</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.9576</v>
+        <v>-2.6284</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.7745</v>
+        <v>-1.7625</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.4158</v>
+        <v>-1.5423</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3587</v>
+        <v>-0.2202</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6456</v>
+        <v>0.0469</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.8486</v>
+        <v>-0.0165</v>
       </c>
       <c r="L7" t="n">
-        <v>0.203</v>
+        <v>0.0634</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.1289</v>
+        <v>-1.8095</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.5672</v>
+        <v>-1.5258</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5617</v>
+        <v>-0.2836</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3582</v>
+        <v>0.7761</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.194</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5523</v>
+        <v>0.7761</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3396</v>
+        <v>0.0059</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8266</v>
+        <v>0.095</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.487</v>
+        <v>-0.0891</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3299</v>
+        <v>-1.8836</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5642</v>
+        <v>-0.3776</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.894</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. OLIVA SANCHEZ</t>
+          <t>M. HERMOSO ALCUBILLA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.8282</v>
+        <v>-2.9494</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7176</v>
+        <v>0.1717</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.1106</v>
+        <v>-3.1212</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.7625</v>
+        <v>-3.7745</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5423</v>
+        <v>-3.4158</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2202</v>
+        <v>-0.3587</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0469</v>
+        <v>-0.6456</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0165</v>
+        <v>-0.8486</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0634</v>
+        <v>0.203</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.8095</v>
+        <v>-3.1289</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.5258</v>
+        <v>-2.5672</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2836</v>
+        <v>-0.5617</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7761</v>
+        <v>1.3582</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.194</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7761</v>
+        <v>1.5523</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0417</v>
+        <v>-0.2033</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.387</v>
+        <v>0.4472</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4287</v>
+        <v>-0.6505</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.8836</v>
+        <v>-0.3299</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3776</v>
+        <v>0.5642</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.506</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="9">
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.1795</v>
+        <v>-5.0979</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4918</v>
+        <v>-2.4102</v>
       </c>
       <c r="F9" t="n">
         <v>-2.6877</v>
@@ -1156,10 +1156,10 @@
         <v>1.1642</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8367</v>
+        <v>-0.7551</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1592</v>
+        <v>0.2408</v>
       </c>
       <c r="U9" t="n">
         <v>-0.9959</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.114</v>
+        <v>-5.3227</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9259</v>
+        <v>-2.3253</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.1881</v>
+        <v>-2.9973</v>
       </c>
       <c r="G10" t="n">
         <v>-3.5921</v>
@@ -1234,13 +1234,13 @@
         <v>0.9702</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1458</v>
+        <v>-0.3544</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.387</v>
+        <v>0.2136</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7588</v>
+        <v>-0.5681</v>
       </c>
       <c r="V10" t="n">
         <v>0.5642</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.3727</v>
+        <v>-6.6271</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.082</v>
+        <v>-4.4999</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2907</v>
+        <v>-2.1272</v>
       </c>
       <c r="G11" t="n">
         <v>-3.9267</v>
@@ -1312,13 +1312,13 @@
         <v>1.1642</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.1341</v>
+        <v>-1.3885</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9444</v>
+        <v>-0.3623</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.1897</v>
+        <v>-1.0262</v>
       </c>
       <c r="V11" t="n">
         <v>-1.506</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-18.7718</v>
+        <v>-17.8635</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.257099999999999</v>
+        <v>-2.348600000000001</v>
       </c>
       <c r="F12" t="n">
         <v>-15.5148</v>
@@ -1369,7 +1369,7 @@
         <v>3.377900000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2228999999999997</v>
+        <v>0.2229000000000001</v>
       </c>
       <c r="M12" t="n">
         <v>-15.5685</v>
@@ -1390,16 +1390,16 @@
         <v>12.6122</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.4565</v>
+        <v>-4.548</v>
       </c>
       <c r="T12" t="n">
-        <v>1.8334</v>
+        <v>2.742</v>
       </c>
       <c r="U12" t="n">
         <v>-7.2899</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3776999999999997</v>
+        <v>-0.3777000000000001</v>
       </c>
       <c r="W12" t="n">
         <v>4.8909</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.856199999999999</v>
+        <v>7.9497</v>
       </c>
       <c r="E13" t="n">
-        <v>9.3348</v>
+        <v>8.4339</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4786</v>
+        <v>-0.4842</v>
       </c>
       <c r="G13" t="n">
         <v>5.5077</v>
@@ -1468,13 +1468,13 @@
         <v>2.1344</v>
       </c>
       <c r="S13" t="n">
-        <v>2.1467</v>
+        <v>1.2402</v>
       </c>
       <c r="T13" t="n">
-        <v>2.2218</v>
+        <v>1.3209</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0751</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>1.0078</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.0773</v>
+        <v>6.2113</v>
       </c>
       <c r="E14" t="n">
-        <v>4.6028</v>
+        <v>4.9031</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4745</v>
+        <v>1.3082</v>
       </c>
       <c r="G14" t="n">
         <v>4.036</v>
@@ -1546,13 +1546,13 @@
         <v>0.9702</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1527</v>
+        <v>-0.0188</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2299</v>
+        <v>0.0704</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0772</v>
+        <v>-0.0891</v>
       </c>
       <c r="V14" t="n">
         <v>1.2239</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.7806</v>
+        <v>5.705</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9638</v>
+        <v>3.8637</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8168</v>
+        <v>1.8413</v>
       </c>
       <c r="G15" t="n">
         <v>4.021</v>
@@ -1624,13 +1624,13 @@
         <v>1.1642</v>
       </c>
       <c r="S15" t="n">
-        <v>1.188</v>
+        <v>1.1123</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1171</v>
+        <v>1.017</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0709</v>
+        <v>0.0954</v>
       </c>
       <c r="V15" t="n">
         <v>0.3776</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3195</v>
+        <v>2.6015</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8091</v>
+        <v>1.6089</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5104</v>
+        <v>0.9926</v>
       </c>
       <c r="G16" t="n">
         <v>1.2834</v>
@@ -1702,13 +1702,13 @@
         <v>0.5821</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1705</v>
+        <v>1.4524</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1776</v>
+        <v>0.9774</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0072</v>
+        <v>0.475</v>
       </c>
       <c r="V16" t="n">
         <v>1.2239</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. SIMON DEL CORRAL</t>
+          <t>N. MAIGA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3776</v>
+        <v>1.7159</v>
       </c>
       <c r="E17" t="n">
-        <v>0.868</v>
+        <v>0.4675</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5097</v>
+        <v>1.2484</v>
       </c>
       <c r="G17" t="n">
-        <v>0.247</v>
+        <v>-2.197</v>
       </c>
       <c r="H17" t="n">
-        <v>0.351</v>
+        <v>1.4517</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.104</v>
+        <v>-3.6487</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4031</v>
+        <v>-1.1222</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3625</v>
+        <v>2.0926</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0406</v>
+        <v>-3.2149</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1561</v>
+        <v>-1.0748</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0115</v>
+        <v>-0.641</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1446</v>
+        <v>-0.4338</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3881</v>
+        <v>0.7761</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5821</v>
+        <v>1.7463</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1707</v>
+        <v>1.5649</v>
       </c>
       <c r="T17" t="n">
-        <v>1.153</v>
+        <v>1.054</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0177</v>
+        <v>0.5109</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3481</v>
+        <v>1.5719</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2821</v>
+        <v>1.506</v>
       </c>
       <c r="X17" t="n">
         <v>0.066</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. MAIGA</t>
+          <t>J. ATIENZA PEREA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.909</v>
+        <v>1.2885</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1672</v>
+        <v>0.3166</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7418</v>
+        <v>0.9719</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.197</v>
+        <v>-0.2792</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4517</v>
+        <v>0.6896</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.6487</v>
+        <v>-0.9688</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1222</v>
+        <v>0.0275</v>
       </c>
       <c r="K18" t="n">
-        <v>2.0926</v>
+        <v>0.7127</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.2149</v>
+        <v>-0.6851</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0748</v>
+        <v>-0.3067</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.641</v>
+        <v>-0.0231</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4338</v>
+        <v>-0.2836</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7761</v>
+        <v>0.9702</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7463</v>
+        <v>0.9702</v>
       </c>
       <c r="S18" t="n">
-        <v>0.758</v>
+        <v>0.5975</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7537</v>
+        <v>0.2891</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0043</v>
+        <v>0.3084</v>
       </c>
       <c r="V18" t="n">
-        <v>1.5719</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.066</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ CAÑAS</t>
+          <t>G. LARDIES GUILLEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3542</v>
+        <v>1.2337</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0778</v>
+        <v>1.8769</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7236</v>
+        <v>-0.6433</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0723</v>
+        <v>1.1596</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3098</v>
+        <v>0.1442</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3821</v>
+        <v>1.0155</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7738</v>
+        <v>1.3938</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7333</v>
+        <v>0.0948</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0406</v>
+        <v>1.2991</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8462</v>
+        <v>-0.2342</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4235</v>
+        <v>0.0494</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4227</v>
+        <v>-0.2836</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5821</v>
+        <v>1.1642</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5821</v>
+        <v>1.1642</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6907</v>
+        <v>0.4158</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3039</v>
+        <v>0.4831</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3867</v>
+        <v>-0.0673</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.8462</v>
+        <v>-1.506</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.8462</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. LARDIES GUILLEN</t>
+          <t>D. FERNANDEZ CAÑAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1025</v>
+        <v>0.6912</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1763</v>
+        <v>1.1779</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0737</v>
+        <v>-0.4867</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1596</v>
+        <v>-0.0723</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1442</v>
+        <v>0.3098</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0155</v>
+        <v>-0.3821</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3938</v>
+        <v>0.7738</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0948</v>
+        <v>0.7333</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2991</v>
+        <v>0.0406</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2342</v>
+        <v>-0.8462</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0494</v>
+        <v>-0.4235</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2836</v>
+        <v>-0.4227</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1642</v>
+        <v>0.5821</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1642</v>
+        <v>0.5821</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7153</v>
+        <v>1.0276</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2176</v>
+        <v>0.404</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4977</v>
+        <v>0.6236</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.506</v>
+        <v>-0.8462</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.506</v>
+        <v>-0.8462</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. ATIENZA PEREA</t>
+          <t>A. SIMON DEL CORRAL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.5496</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3841</v>
+        <v>0.0672</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3835</v>
+        <v>0.4824</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2792</v>
+        <v>0.247</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6896</v>
+        <v>0.351</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9688</v>
+        <v>-0.104</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0275</v>
+        <v>0.4031</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7127</v>
+        <v>0.3625</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6851</v>
+        <v>0.0406</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3067</v>
+        <v>-0.1561</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0231</v>
+        <v>-0.0115</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2836</v>
+        <v>-0.1446</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9702</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9702</v>
+        <v>0.5821</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6916</v>
+        <v>0.3426</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4116</v>
+        <v>0.3522</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2799</v>
+        <v>-0.0095</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.3481</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2258</v>
+        <v>-0.0985</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1411</v>
+        <v>-0.041</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0847</v>
+        <v>-0.0575</v>
       </c>
       <c r="G22" t="n">
         <v>-0.5769</v>
@@ -2170,13 +2170,13 @@
         <v>0.5821</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.297</v>
+        <v>-0.1696</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1817</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1153</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>0.066</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2545</v>
+        <v>-1.7879</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2238</v>
+        <v>-3.3239</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9692</v>
+        <v>1.536</v>
       </c>
       <c r="G23" t="n">
         <v>-1.6303</v>
@@ -2248,13 +2248,13 @@
         <v>2.1344</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2723</v>
+        <v>0.1943</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6808</v>
+        <v>0.5807</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9530999999999999</v>
+        <v>-0.3864</v>
       </c>
       <c r="V23" t="n">
         <v>-0.546</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.5242</v>
+        <v>-3.9513</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.7359</v>
+        <v>-3.836</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7882</v>
+        <v>-0.1153</v>
       </c>
       <c r="G24" t="n">
         <v>0.4686</v>
@@ -2326,13 +2326,13 @@
         <v>0.9702</v>
       </c>
       <c r="S24" t="n">
-        <v>0.461</v>
+        <v>1.0338</v>
       </c>
       <c r="T24" t="n">
-        <v>0.923</v>
+        <v>0.8229</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4621</v>
+        <v>0.2109</v>
       </c>
       <c r="V24" t="n">
         <v>-2.5433</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>18.7718</v>
+        <v>22.1087</v>
       </c>
       <c r="E25" t="n">
-        <v>15.5149</v>
+        <v>15.5148</v>
       </c>
       <c r="F25" t="n">
-        <v>3.257099999999999</v>
+        <v>6.593799999999999</v>
       </c>
       <c r="G25" t="n">
         <v>11.9676</v>
@@ -2383,7 +2383,7 @@
         <v>16.7082</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.1398</v>
+        <v>-1.139800000000001</v>
       </c>
       <c r="M25" t="n">
         <v>-3.6007</v>
@@ -2392,10 +2392,10 @@
         <v>-3.378</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.2227</v>
+        <v>-0.2227000000000002</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9701</v>
+        <v>0.9700999999999995</v>
       </c>
       <c r="Q25" t="n">
         <v>-12.6121</v>
@@ -2404,16 +2404,16 @@
         <v>13.5825</v>
       </c>
       <c r="S25" t="n">
-        <v>5.456700000000001</v>
+        <v>8.792999999999999</v>
       </c>
       <c r="T25" t="n">
         <v>7.2901</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.8336</v>
+        <v>1.5032</v>
       </c>
       <c r="V25" t="n">
-        <v>0.3776999999999995</v>
+        <v>0.3777000000000004</v>
       </c>
       <c r="W25" t="n">
         <v>5.268599999999999</v>
